--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Giudici popolari.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Giudici popolari.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="88">
   <si>
     <r>
       <t xml:space="preserve">
@@ -149,7 +149,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Fai richiesta di iscrizione</t>
+    <t>Iscriviti</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -403,7 +403,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 Hai tempo fino al </t>
     </r>
     <r>
@@ -449,7 +449,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -675,13 +675,10 @@
     </r>
   </si>
   <si>
-    <t>-</t>
+    <t>Fai domanda</t>
   </si>
   <si>
     <t>Vai alle liste</t>
-  </si>
-  <si>
-    <t>Vai alla lista</t>
   </si>
   <si>
     <t>Vai all’albo</t>
@@ -704,7 +701,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -714,6 +711,9 @@
   </si>
   <si>
     <t>&lt;modulo d'iscrizione&gt;</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <r>
@@ -766,10 +766,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
   </si>
 </sst>
 </file>
@@ -1434,15 +1430,15 @@
         <v>73</v>
       </c>
       <c r="D6" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="34" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>54</v>
@@ -1459,19 +1455,19 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="C8" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="34" t="s">
-        <v>72</v>
-      </c>
       <c r="D8" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1513,7 +1509,7 @@
         <v>87</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="C11" s="34" t="s">
         <v>54</v>
